--- a/sourcedata/KPI_Territory.xlsx
+++ b/sourcedata/KPI_Territory.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB61"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,8 @@
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="14" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -601,6 +603,16 @@
           <t>VERITONEX_NRx</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>CLAROZEPT_NRx</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>DEPTRAZOL_NRx</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -637,67 +649,73 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1430</v>
+        <v>1121</v>
       </c>
       <c r="I2" t="n">
-        <v>312</v>
+        <v>208</v>
       </c>
       <c r="J2" t="n">
-        <v>1429</v>
+        <v>1084</v>
       </c>
       <c r="K2" t="n">
-        <v>317</v>
+        <v>194</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>8.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="N2" t="n">
-        <v>9.15</v>
+        <v>9.77</v>
       </c>
       <c r="O2" t="n">
-        <v>17030</v>
+        <v>12711</v>
       </c>
       <c r="P2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q2" t="n">
-        <v>101.2</v>
+        <v>100.3</v>
       </c>
       <c r="R2" t="n">
-        <v>101.2</v>
+        <v>100.3</v>
       </c>
       <c r="S2" t="n">
-        <v>214</v>
+        <v>149</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="X2" t="n">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="Y2" t="n">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="Z2" t="n">
-        <v>465</v>
+        <v>277</v>
       </c>
       <c r="AA2" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>73</v>
+        <v>66</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -735,67 +753,73 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="I3" t="n">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="J3" t="n">
-        <v>1296</v>
+        <v>1236</v>
       </c>
       <c r="K3" t="n">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="M3" t="n">
-        <v>8.81</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>9.24</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>14528</v>
+        <v>16050</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="n">
-        <v>107.1</v>
+        <v>102.7</v>
       </c>
       <c r="R3" t="n">
-        <v>107.1</v>
+        <v>102.7</v>
       </c>
       <c r="S3" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="V3" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="W3" t="n">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="X3" t="n">
-        <v>295</v>
+        <v>430</v>
       </c>
       <c r="Y3" t="n">
-        <v>329</v>
+        <v>191</v>
       </c>
       <c r="Z3" t="n">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AB3" t="n">
-        <v>58</v>
+        <v>91</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>39</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="4">
@@ -833,67 +857,73 @@
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1847</v>
+        <v>1174</v>
       </c>
       <c r="I4" t="n">
-        <v>378</v>
+        <v>257</v>
       </c>
       <c r="J4" t="n">
-        <v>1863</v>
+        <v>1152</v>
       </c>
       <c r="K4" t="n">
-        <v>374</v>
+        <v>256</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9</v>
+        <v>1.9</v>
       </c>
       <c r="M4" t="n">
-        <v>8.76</v>
+        <v>8.44</v>
       </c>
       <c r="N4" t="n">
-        <v>8.949999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="O4" t="n">
-        <v>22221</v>
+        <v>14954</v>
       </c>
       <c r="P4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="n">
-        <v>101.5</v>
+        <v>94.7</v>
       </c>
       <c r="R4" t="n">
-        <v>101.5</v>
+        <v>94.7</v>
       </c>
       <c r="S4" t="n">
-        <v>287</v>
+        <v>187</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>3.43</v>
       </c>
       <c r="W4" t="n">
-        <v>429</v>
+        <v>217</v>
       </c>
       <c r="X4" t="n">
-        <v>393</v>
+        <v>348</v>
       </c>
       <c r="Y4" t="n">
-        <v>551</v>
+        <v>308</v>
       </c>
       <c r="Z4" t="n">
-        <v>474</v>
+        <v>301</v>
       </c>
       <c r="AA4" t="n">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="AB4" t="n">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>82</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -931,67 +961,73 @@
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1415</v>
+        <v>604</v>
       </c>
       <c r="I5" t="n">
-        <v>271</v>
+        <v>111</v>
       </c>
       <c r="J5" t="n">
-        <v>1437</v>
+        <v>597</v>
       </c>
       <c r="K5" t="n">
-        <v>265</v>
+        <v>108</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.5</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="N5" t="n">
-        <v>9.92</v>
+        <v>8.66</v>
       </c>
       <c r="O5" t="n">
-        <v>15825</v>
+        <v>6496</v>
       </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>98.5</v>
+        <v>95.2</v>
       </c>
       <c r="R5" t="n">
-        <v>98.5</v>
+        <v>95.2</v>
       </c>
       <c r="S5" t="n">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V5" t="n">
-        <v>5.75</v>
+        <v>2.78</v>
       </c>
       <c r="W5" t="n">
-        <v>333</v>
+        <v>159</v>
       </c>
       <c r="X5" t="n">
-        <v>293</v>
+        <v>165</v>
       </c>
       <c r="Y5" t="n">
-        <v>417</v>
+        <v>138</v>
       </c>
       <c r="Z5" t="n">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="AA5" t="n">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="AB5" t="n">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -1029,67 +1065,73 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1616</v>
+        <v>1066</v>
       </c>
       <c r="I6" t="n">
-        <v>316</v>
+        <v>213</v>
       </c>
       <c r="J6" t="n">
-        <v>1568</v>
+        <v>1019</v>
       </c>
       <c r="K6" t="n">
-        <v>307</v>
+        <v>213</v>
       </c>
       <c r="L6" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="M6" t="n">
-        <v>9.34</v>
+        <v>8.77</v>
       </c>
       <c r="N6" t="n">
-        <v>9.07</v>
+        <v>7.82</v>
       </c>
       <c r="O6" t="n">
-        <v>17132</v>
+        <v>12287</v>
       </c>
       <c r="P6" t="n">
         <v>22</v>
       </c>
       <c r="Q6" t="n">
-        <v>95.8</v>
+        <v>93.3</v>
       </c>
       <c r="R6" t="n">
-        <v>95.8</v>
+        <v>93.3</v>
       </c>
       <c r="S6" t="n">
-        <v>223</v>
+        <v>150</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U6" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>3.14</v>
       </c>
       <c r="W6" t="n">
-        <v>394</v>
+        <v>324</v>
       </c>
       <c r="X6" t="n">
-        <v>432</v>
+        <v>303</v>
       </c>
       <c r="Y6" t="n">
-        <v>445</v>
+        <v>201</v>
       </c>
       <c r="Z6" t="n">
-        <v>345</v>
+        <v>238</v>
       </c>
       <c r="AA6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AB6" t="n">
-        <v>100</v>
+        <v>85</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -1127,67 +1169,73 @@
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>1374</v>
+        <v>1117</v>
       </c>
       <c r="I7" t="n">
-        <v>305</v>
+        <v>190</v>
       </c>
       <c r="J7" t="n">
-        <v>1355</v>
+        <v>1174</v>
       </c>
       <c r="K7" t="n">
-        <v>306</v>
+        <v>167</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>-4.9</v>
       </c>
       <c r="M7" t="n">
-        <v>9.210000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="N7" t="n">
-        <v>8.59</v>
+        <v>10.08</v>
       </c>
       <c r="O7" t="n">
-        <v>16895</v>
+        <v>11753</v>
       </c>
       <c r="P7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.2</v>
+        <v>103.2</v>
       </c>
       <c r="R7" t="n">
-        <v>94.2</v>
+        <v>103.2</v>
       </c>
       <c r="S7" t="n">
-        <v>225</v>
+        <v>138</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U7" t="n">
         <v>100</v>
       </c>
       <c r="V7" t="n">
-        <v>5.75</v>
+        <v>2.1</v>
       </c>
       <c r="W7" t="n">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="X7" t="n">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="Y7" t="n">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="Z7" t="n">
-        <v>394</v>
+        <v>204</v>
       </c>
       <c r="AA7" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="AB7" t="n">
-        <v>87</v>
+        <v>67</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -1225,67 +1273,73 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>976</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>986</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M8" t="n">
-        <v/>
+        <v>9.27</v>
       </c>
       <c r="N8" t="n">
-        <v/>
+        <v>7.62</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>11051</v>
       </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U8" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="V8" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -1323,67 +1377,73 @@
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1264</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1263</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M9" t="n">
-        <v/>
+        <v>8.94</v>
       </c>
       <c r="N9" t="n">
-        <v/>
+        <v>8.460000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>14481</v>
       </c>
       <c r="P9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>102.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>102.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U9" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="V9" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -1421,67 +1481,73 @@
         <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1103</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1049</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M10" t="n">
-        <v/>
+        <v>9.470000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v/>
+        <v>8.66</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>12429</v>
       </c>
       <c r="P10" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>125</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="n">
+        <v>90</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W10" t="n">
+        <v>321</v>
+      </c>
+      <c r="X10" t="n">
+        <v>161</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>263</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>358</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB10" t="n">
         <v>28</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>500</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
+      <c r="AC10" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -1519,67 +1585,73 @@
         <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="M11" t="n">
-        <v/>
+        <v>9.630000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v/>
+        <v>9.59</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>8841</v>
       </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>90.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>90.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U11" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="V11" t="n">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1617,67 +1689,73 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M12" t="n">
-        <v/>
+        <v>9.470000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v/>
+        <v>9.68</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>9186</v>
       </c>
       <c r="P12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U12" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="V12" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>32</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -1715,67 +1793,73 @@
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1004</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v/>
+        <v>8.609999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v/>
+        <v>8.949999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>12445</v>
       </c>
       <c r="P13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>104.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>104.3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U13" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="V13" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -1813,67 +1897,73 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1338</v>
+        <v>1274</v>
       </c>
       <c r="I14" t="n">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="J14" t="n">
-        <v>1317</v>
+        <v>1331</v>
       </c>
       <c r="K14" t="n">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>-4.3</v>
       </c>
       <c r="M14" t="n">
-        <v>9.15</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>9.69</v>
+        <v>9.85</v>
       </c>
       <c r="O14" t="n">
-        <v>14914</v>
+        <v>15002</v>
       </c>
       <c r="P14" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q14" t="n">
-        <v>94.5</v>
+        <v>102.4</v>
       </c>
       <c r="R14" t="n">
-        <v>94.5</v>
+        <v>102.4</v>
       </c>
       <c r="S14" t="n">
         <v>183</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U14" t="n">
         <v>100</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="W14" t="n">
-        <v>369</v>
+        <v>179</v>
       </c>
       <c r="X14" t="n">
-        <v>301</v>
+        <v>230</v>
       </c>
       <c r="Y14" t="n">
-        <v>284</v>
+        <v>478</v>
       </c>
       <c r="Z14" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AA14" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="AB14" t="n">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>74</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -1911,67 +2001,73 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>1394</v>
+        <v>1154</v>
       </c>
       <c r="I15" t="n">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="J15" t="n">
-        <v>1377</v>
+        <v>1126</v>
       </c>
       <c r="K15" t="n">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>9.890000000000001</v>
+        <v>10.28</v>
       </c>
       <c r="N15" t="n">
-        <v>9.42</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>14040</v>
+        <v>11423</v>
       </c>
       <c r="P15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q15" t="n">
-        <v>92.40000000000001</v>
+        <v>101.7</v>
       </c>
       <c r="R15" t="n">
-        <v>92.40000000000001</v>
+        <v>101.7</v>
       </c>
       <c r="S15" t="n">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U15" t="n">
         <v>100</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>1.9</v>
       </c>
       <c r="W15" t="n">
-        <v>431</v>
+        <v>172</v>
       </c>
       <c r="X15" t="n">
-        <v>376</v>
+        <v>158</v>
       </c>
       <c r="Y15" t="n">
-        <v>244</v>
+        <v>359</v>
       </c>
       <c r="Z15" t="n">
-        <v>343</v>
+        <v>465</v>
       </c>
       <c r="AA15" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="AB15" t="n">
-        <v>82</v>
+        <v>35</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>76</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="16">
@@ -2009,67 +2105,73 @@
         <v>3</v>
       </c>
       <c r="H16" t="n">
-        <v>766</v>
+        <v>1188</v>
       </c>
       <c r="I16" t="n">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="J16" t="n">
-        <v>784</v>
+        <v>1184</v>
       </c>
       <c r="K16" t="n">
-        <v>164</v>
+        <v>209</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.3</v>
+        <v>0.3</v>
       </c>
       <c r="M16" t="n">
-        <v>9.18</v>
+        <v>8.6</v>
       </c>
       <c r="N16" t="n">
-        <v>10.13</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>8379</v>
+        <v>15304</v>
       </c>
       <c r="P16" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q16" t="n">
-        <v>94.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>94.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U16" t="n">
         <v>100</v>
       </c>
       <c r="V16" t="n">
-        <v>6.33</v>
+        <v>2.6</v>
       </c>
       <c r="W16" t="n">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="X16" t="n">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="Y16" t="n">
-        <v>167</v>
+        <v>425</v>
       </c>
       <c r="Z16" t="n">
-        <v>221</v>
+        <v>502</v>
       </c>
       <c r="AA16" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AB16" t="n">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -2107,67 +2209,73 @@
         <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>953</v>
+        <v>1193</v>
       </c>
       <c r="I17" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="J17" t="n">
-        <v>949</v>
+        <v>1103</v>
       </c>
       <c r="K17" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>9.220000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="N17" t="n">
-        <v>9.630000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="O17" t="n">
-        <v>10553</v>
+        <v>14067</v>
       </c>
       <c r="P17" t="n">
         <v>21</v>
       </c>
       <c r="Q17" t="n">
-        <v>98.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="R17" t="n">
-        <v>98.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="S17" t="n">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U17" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>2.62</v>
       </c>
       <c r="W17" t="n">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="X17" t="n">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="Y17" t="n">
-        <v>287</v>
+        <v>408</v>
       </c>
       <c r="Z17" t="n">
-        <v>197</v>
+        <v>429</v>
       </c>
       <c r="AA17" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>39</v>
+        <v>26</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>71</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="18">
@@ -2205,67 +2313,73 @@
         <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>586</v>
+        <v>1041</v>
       </c>
       <c r="I18" t="n">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="J18" t="n">
-        <v>610</v>
+        <v>1041</v>
       </c>
       <c r="K18" t="n">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>9.460000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="O18" t="n">
-        <v>6293</v>
+        <v>11988</v>
       </c>
       <c r="P18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q18" t="n">
-        <v>94.7</v>
+        <v>93.3</v>
       </c>
       <c r="R18" t="n">
-        <v>94.7</v>
+        <v>93.3</v>
       </c>
       <c r="S18" t="n">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U18" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V18" t="n">
-        <v>6.67</v>
+        <v>2.56</v>
       </c>
       <c r="W18" t="n">
-        <v>162</v>
+        <v>242</v>
       </c>
       <c r="X18" t="n">
-        <v>154</v>
+        <v>266</v>
       </c>
       <c r="Y18" t="n">
-        <v>134</v>
+        <v>312</v>
       </c>
       <c r="Z18" t="n">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="AA18" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="AB18" t="n">
-        <v>29</v>
+        <v>50</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>53</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="19">
@@ -2303,67 +2417,73 @@
         <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>1412</v>
+        <v>1353</v>
       </c>
       <c r="I19" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="J19" t="n">
-        <v>1430</v>
+        <v>1348</v>
       </c>
       <c r="K19" t="n">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3</v>
+        <v>0.4</v>
       </c>
       <c r="M19" t="n">
-        <v>9.279999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>9.44</v>
+        <v>9.25</v>
       </c>
       <c r="O19" t="n">
-        <v>15981</v>
+        <v>15438</v>
       </c>
       <c r="P19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q19" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="R19" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="S19" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="T19" t="n">
+        <v>10</v>
+      </c>
+      <c r="U19" t="n">
+        <v>90</v>
+      </c>
+      <c r="V19" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
-        <v>100</v>
-      </c>
-      <c r="V19" t="n">
-        <v>8.33</v>
-      </c>
       <c r="W19" t="n">
-        <v>455</v>
+        <v>217</v>
       </c>
       <c r="X19" t="n">
-        <v>299</v>
+        <v>196</v>
       </c>
       <c r="Y19" t="n">
-        <v>395</v>
+        <v>495</v>
       </c>
       <c r="Z19" t="n">
-        <v>263</v>
+        <v>445</v>
       </c>
       <c r="AA19" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="AB19" t="n">
-        <v>38</v>
+        <v>24</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>74</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="20">
@@ -2401,67 +2521,73 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>172</v>
+        <v>667</v>
       </c>
       <c r="I20" t="n">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="J20" t="n">
-        <v>172</v>
+        <v>664</v>
       </c>
       <c r="K20" t="n">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M20" t="n">
-        <v>8.73</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>7.66</v>
+        <v>9.33</v>
       </c>
       <c r="O20" t="n">
-        <v>1961</v>
+        <v>7328</v>
       </c>
       <c r="P20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q20" t="n">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="R20" t="n">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="S20" t="n">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U20" t="n">
+        <v>90</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W20" t="n">
         <v>100</v>
       </c>
-      <c r="V20" t="n">
-        <v>13</v>
-      </c>
-      <c r="W20" t="n">
-        <v>46</v>
-      </c>
       <c r="X20" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="Y20" t="n">
-        <v>52</v>
+        <v>296</v>
       </c>
       <c r="Z20" t="n">
-        <v>37</v>
+        <v>199</v>
       </c>
       <c r="AA20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB20" t="n">
         <v>11</v>
       </c>
-      <c r="AB20" t="n">
-        <v>4</v>
+      <c r="AC20" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -2499,67 +2625,73 @@
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>287</v>
+        <v>547</v>
       </c>
       <c r="I21" t="n">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="J21" t="n">
-        <v>288</v>
+        <v>553</v>
       </c>
       <c r="K21" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="M21" t="n">
-        <v>8.859999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>7.82</v>
+        <v>8.58</v>
       </c>
       <c r="O21" t="n">
-        <v>3444</v>
+        <v>6272</v>
       </c>
       <c r="P21" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q21" t="n">
-        <v>95.2</v>
+        <v>93.2</v>
       </c>
       <c r="R21" t="n">
-        <v>95.2</v>
+        <v>93.2</v>
       </c>
       <c r="S21" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U21" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V21" t="n">
-        <v>9</v>
+        <v>2.78</v>
       </c>
       <c r="W21" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="X21" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="Y21" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="Z21" t="n">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="AA21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AB21" t="n">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>41</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -2597,67 +2729,73 @@
         <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>273</v>
+        <v>672</v>
       </c>
       <c r="I22" t="n">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="J22" t="n">
-        <v>266</v>
+        <v>667</v>
       </c>
       <c r="K22" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="M22" t="n">
-        <v>10.12</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>8.960000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>2741</v>
+        <v>7647</v>
       </c>
       <c r="P22" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q22" t="n">
-        <v>96.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="R22" t="n">
-        <v>96.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="S22" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U22" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V22" t="n">
-        <v>9.5</v>
+        <v>2.56</v>
       </c>
       <c r="W22" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="X22" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="Y22" t="n">
-        <v>67</v>
+        <v>209</v>
       </c>
       <c r="Z22" t="n">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="AA22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AB22" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -2695,67 +2833,73 @@
         <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>186</v>
+        <v>738</v>
       </c>
       <c r="I23" t="n">
-        <v>32</v>
+        <v>154</v>
       </c>
       <c r="J23" t="n">
-        <v>187</v>
+        <v>718</v>
       </c>
       <c r="K23" t="n">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>7.88</v>
+        <v>8.24</v>
       </c>
       <c r="N23" t="n">
-        <v>8.65</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>2504</v>
+        <v>8607</v>
       </c>
       <c r="P23" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q23" t="n">
-        <v>99.5</v>
+        <v>92.3</v>
       </c>
       <c r="R23" t="n">
-        <v>99.5</v>
+        <v>92.3</v>
       </c>
       <c r="S23" t="n">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U23" t="n">
         <v>100</v>
       </c>
       <c r="V23" t="n">
-        <v>14</v>
+        <v>2.3</v>
       </c>
       <c r="W23" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="X23" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="Y23" t="n">
-        <v>46</v>
+        <v>344</v>
       </c>
       <c r="Z23" t="n">
-        <v>59</v>
+        <v>220</v>
       </c>
       <c r="AA23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AB23" t="n">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="24">
@@ -2793,67 +2937,73 @@
         <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>151</v>
+        <v>669</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="J24" t="n">
-        <v>141</v>
+        <v>661</v>
       </c>
       <c r="K24" t="n">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="L24" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="M24" t="n">
-        <v>10.03</v>
+        <v>9.52</v>
       </c>
       <c r="N24" t="n">
-        <v>8.83</v>
+        <v>8.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1611</v>
+        <v>7519</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q24" t="n">
-        <v>106.4</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R24" t="n">
-        <v>106.4</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U24" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V24" t="n">
-        <v>11.5</v>
+        <v>2.44</v>
       </c>
       <c r="W24" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="X24" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="Y24" t="n">
-        <v>41</v>
+        <v>241</v>
       </c>
       <c r="Z24" t="n">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="AA24" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AB24" t="n">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>56</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -2891,67 +3041,73 @@
         <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>242</v>
+        <v>653</v>
       </c>
       <c r="I25" t="n">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="J25" t="n">
-        <v>225</v>
+        <v>655</v>
       </c>
       <c r="K25" t="n">
+        <v>109</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="O25" t="n">
+        <v>7824</v>
+      </c>
+      <c r="P25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>92</v>
+      </c>
+      <c r="R25" t="n">
+        <v>92</v>
+      </c>
+      <c r="S25" t="n">
+        <v>84</v>
+      </c>
+      <c r="T25" t="n">
+        <v>10</v>
+      </c>
+      <c r="U25" t="n">
+        <v>80</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>122</v>
+      </c>
+      <c r="X25" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>210</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>261</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD25" t="n">
         <v>47</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M25" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="N25" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2821</v>
-      </c>
-      <c r="P25" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>103.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>103.6</v>
-      </c>
-      <c r="S25" t="n">
-        <v>31</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>100</v>
-      </c>
-      <c r="V25" t="n">
-        <v>13</v>
-      </c>
-      <c r="W25" t="n">
-        <v>77</v>
-      </c>
-      <c r="X25" t="n">
-        <v>39</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>69</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -2989,67 +3145,73 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>213</v>
+        <v>790</v>
       </c>
       <c r="I26" t="n">
-        <v>42</v>
+        <v>163</v>
       </c>
       <c r="J26" t="n">
-        <v>221</v>
+        <v>765</v>
       </c>
       <c r="K26" t="n">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.6</v>
+        <v>3.3</v>
       </c>
       <c r="M26" t="n">
-        <v>9.6</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>9.140000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="O26" t="n">
-        <v>2224</v>
+        <v>8811</v>
       </c>
       <c r="P26" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q26" t="n">
-        <v>97.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>97.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U26" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V26" t="n">
-        <v>13</v>
+        <v>2.11</v>
       </c>
       <c r="W26" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="X26" t="n">
+        <v>174</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>259</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>243</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC26" t="n">
         <v>63</v>
       </c>
-      <c r="Y26" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>15</v>
+      <c r="AD26" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="27">
@@ -3087,67 +3249,73 @@
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>251</v>
+        <v>997</v>
       </c>
       <c r="I27" t="n">
-        <v>50</v>
+        <v>183</v>
       </c>
       <c r="J27" t="n">
-        <v>252</v>
+        <v>983</v>
       </c>
       <c r="K27" t="n">
-        <v>46</v>
+        <v>185</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.4</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>8.18</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>9.98</v>
+        <v>8.65</v>
       </c>
       <c r="O27" t="n">
-        <v>3026</v>
+        <v>12052</v>
       </c>
       <c r="P27" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q27" t="n">
-        <v>89.5</v>
+        <v>104.2</v>
       </c>
       <c r="R27" t="n">
-        <v>89.5</v>
+        <v>104.2</v>
       </c>
       <c r="S27" t="n">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U27" t="n">
         <v>100</v>
       </c>
       <c r="V27" t="n">
-        <v>10.5</v>
+        <v>2.7</v>
       </c>
       <c r="W27" t="n">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="X27" t="n">
-        <v>36</v>
+        <v>215</v>
       </c>
       <c r="Y27" t="n">
-        <v>71</v>
+        <v>340</v>
       </c>
       <c r="Z27" t="n">
-        <v>50</v>
+        <v>307</v>
       </c>
       <c r="AA27" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AB27" t="n">
-        <v>7</v>
+        <v>32</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="28">
@@ -3185,67 +3353,73 @@
         <v>3</v>
       </c>
       <c r="H28" t="n">
+        <v>690</v>
+      </c>
+      <c r="I28" t="n">
+        <v>122</v>
+      </c>
+      <c r="J28" t="n">
+        <v>703</v>
+      </c>
+      <c r="K28" t="n">
+        <v>116</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="N28" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="O28" t="n">
+        <v>8773</v>
+      </c>
+      <c r="P28" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>76</v>
+      </c>
+      <c r="T28" t="n">
+        <v>10</v>
+      </c>
+      <c r="U28" t="n">
+        <v>70</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W28" t="n">
+        <v>90</v>
+      </c>
+      <c r="X28" t="n">
         <v>170</v>
       </c>
-      <c r="I28" t="n">
-        <v>28</v>
-      </c>
-      <c r="J28" t="n">
-        <v>165</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="Y28" t="n">
+        <v>213</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>217</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AC28" t="n">
         <v>24</v>
       </c>
-      <c r="L28" t="n">
-        <v>3</v>
-      </c>
-      <c r="M28" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="N28" t="n">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1861</v>
-      </c>
-      <c r="P28" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="R28" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>16</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>100</v>
-      </c>
-      <c r="V28" t="n">
-        <v>11</v>
-      </c>
-      <c r="W28" t="n">
-        <v>47</v>
-      </c>
-      <c r="X28" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AD28" t="n">
         <v>45</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -3283,67 +3457,73 @@
         <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>177</v>
+        <v>662</v>
       </c>
       <c r="I29" t="n">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="J29" t="n">
-        <v>170</v>
+        <v>709</v>
       </c>
       <c r="K29" t="n">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="L29" t="n">
-        <v>4.1</v>
+        <v>-6.6</v>
       </c>
       <c r="M29" t="n">
-        <v>9.84</v>
+        <v>9.17</v>
       </c>
       <c r="N29" t="n">
-        <v>9.029999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="O29" t="n">
-        <v>1800</v>
+        <v>7528</v>
       </c>
       <c r="P29" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q29" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="R29" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U29" t="n">
         <v>100</v>
       </c>
       <c r="V29" t="n">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="W29" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="X29" t="n">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="Y29" t="n">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="Z29" t="n">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="AA29" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AB29" t="n">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="30">
@@ -3381,67 +3561,73 @@
         <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>259</v>
+        <v>608</v>
       </c>
       <c r="I30" t="n">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="J30" t="n">
-        <v>254</v>
+        <v>599</v>
       </c>
       <c r="K30" t="n">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
-        <v>9.869999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="N30" t="n">
-        <v>10.29</v>
+        <v>9.66</v>
       </c>
       <c r="O30" t="n">
-        <v>2728</v>
+        <v>7789</v>
       </c>
       <c r="P30" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>78</v>
+      </c>
+      <c r="T30" t="n">
+        <v>10</v>
+      </c>
+      <c r="U30" t="n">
+        <v>80</v>
+      </c>
+      <c r="V30" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="W30" t="n">
+        <v>143</v>
+      </c>
+      <c r="X30" t="n">
+        <v>154</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>150</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>161</v>
+      </c>
+      <c r="AA30" t="n">
         <v>24</v>
       </c>
-      <c r="Q30" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>35</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>100</v>
-      </c>
-      <c r="V30" t="n">
-        <v>12</v>
-      </c>
-      <c r="W30" t="n">
-        <v>75</v>
-      </c>
-      <c r="X30" t="n">
-        <v>62</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>52</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>16</v>
-      </c>
       <c r="AB30" t="n">
-        <v>13</v>
+        <v>26</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="31">
@@ -3479,67 +3665,73 @@
         <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>367</v>
+        <v>1081</v>
       </c>
       <c r="I31" t="n">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="J31" t="n">
-        <v>367</v>
+        <v>1068</v>
       </c>
       <c r="K31" t="n">
-        <v>65</v>
+        <v>202</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M31" t="n">
-        <v>8.640000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>9.02</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>4390</v>
+        <v>11385</v>
       </c>
       <c r="P31" t="n">
         <v>24</v>
       </c>
       <c r="Q31" t="n">
-        <v>95.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R31" t="n">
-        <v>95.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S31" t="n">
-        <v>49</v>
+        <v>137</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U31" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V31" t="n">
-        <v>12</v>
+        <v>2.67</v>
       </c>
       <c r="W31" t="n">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="X31" t="n">
-        <v>113</v>
+        <v>242</v>
       </c>
       <c r="Y31" t="n">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="Z31" t="n">
-        <v>71</v>
+        <v>324</v>
       </c>
       <c r="AA31" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="AB31" t="n">
-        <v>20</v>
+        <v>38</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>69</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="32">
@@ -3577,67 +3769,73 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>306</v>
+        <v>588</v>
       </c>
       <c r="I32" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="J32" t="n">
-        <v>291</v>
+        <v>621</v>
       </c>
       <c r="K32" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="L32" t="n">
-        <v>5.2</v>
+        <v>-5.3</v>
       </c>
       <c r="M32" t="n">
-        <v>9.24</v>
+        <v>9.35</v>
       </c>
       <c r="N32" t="n">
-        <v>8.98</v>
+        <v>8.17</v>
       </c>
       <c r="O32" t="n">
-        <v>3075</v>
+        <v>6410</v>
       </c>
       <c r="P32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q32" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="R32" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="S32" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U32" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V32" t="n">
-        <v>12</v>
+        <v>2.78</v>
       </c>
       <c r="W32" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="X32" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="Y32" t="n">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="Z32" t="n">
-        <v>61</v>
+        <v>205</v>
       </c>
       <c r="AA32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB32" t="n">
         <v>15</v>
       </c>
-      <c r="AB32" t="n">
-        <v>16</v>
+      <c r="AC32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="33">
@@ -3675,67 +3873,73 @@
         <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>225</v>
+        <v>471</v>
       </c>
       <c r="I33" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="J33" t="n">
-        <v>220</v>
+        <v>481</v>
       </c>
       <c r="K33" t="n">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="M33" t="n">
-        <v>7.89</v>
+        <v>8.26</v>
       </c>
       <c r="N33" t="n">
-        <v>6.91</v>
+        <v>8.35</v>
       </c>
       <c r="O33" t="n">
-        <v>2916</v>
+        <v>5839</v>
       </c>
       <c r="P33" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>66</v>
+      </c>
+      <c r="T33" t="n">
+        <v>10</v>
+      </c>
+      <c r="U33" t="n">
+        <v>80</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W33" t="n">
+        <v>92</v>
+      </c>
+      <c r="X33" t="n">
+        <v>91</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>145</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>143</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB33" t="n">
         <v>21</v>
       </c>
-      <c r="Q33" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="R33" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="S33" t="n">
-        <v>21</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>100</v>
-      </c>
-      <c r="V33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>59</v>
-      </c>
-      <c r="X33" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>62</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>5</v>
+      <c r="AC33" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="34">
@@ -3773,67 +3977,73 @@
         <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>290</v>
+        <v>570</v>
       </c>
       <c r="I34" t="n">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="J34" t="n">
-        <v>302</v>
+        <v>575</v>
       </c>
       <c r="K34" t="n">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="L34" t="n">
-        <v>-4</v>
+        <v>-0.9</v>
       </c>
       <c r="M34" t="n">
-        <v>9.74</v>
+        <v>8.41</v>
       </c>
       <c r="N34" t="n">
-        <v>8.23</v>
+        <v>9.34</v>
       </c>
       <c r="O34" t="n">
-        <v>3294</v>
+        <v>6876</v>
       </c>
       <c r="P34" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Q34" t="n">
-        <v>97.3</v>
+        <v>103</v>
       </c>
       <c r="R34" t="n">
-        <v>97.3</v>
+        <v>103</v>
       </c>
       <c r="S34" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="T34" t="n">
+        <v>10</v>
+      </c>
+      <c r="U34" t="n">
+        <v>90</v>
+      </c>
+      <c r="V34" t="n">
         <v>2</v>
       </c>
-      <c r="U34" t="n">
-        <v>100</v>
-      </c>
-      <c r="V34" t="n">
-        <v>14</v>
-      </c>
       <c r="W34" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="X34" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="Y34" t="n">
-        <v>94</v>
+        <v>236</v>
       </c>
       <c r="Z34" t="n">
-        <v>53</v>
+        <v>228</v>
       </c>
       <c r="AA34" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AB34" t="n">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="35">
@@ -3871,67 +4081,73 @@
         <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>192</v>
+        <v>615</v>
       </c>
       <c r="I35" t="n">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="J35" t="n">
-        <v>185</v>
+        <v>622</v>
       </c>
       <c r="K35" t="n">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="L35" t="n">
-        <v>3.8</v>
+        <v>-1.1</v>
       </c>
       <c r="M35" t="n">
-        <v>8.869999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="N35" t="n">
-        <v>9.09</v>
+        <v>8.67</v>
       </c>
       <c r="O35" t="n">
-        <v>2174</v>
+        <v>6425</v>
       </c>
       <c r="P35" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q35" t="n">
-        <v>107.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="R35" t="n">
-        <v>107.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="S35" t="n">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U35" t="n">
         <v>100</v>
       </c>
       <c r="V35" t="n">
-        <v>12</v>
+        <v>1.8</v>
       </c>
       <c r="W35" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="X35" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="Y35" t="n">
-        <v>69</v>
+        <v>250</v>
       </c>
       <c r="Z35" t="n">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="AA35" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AB35" t="n">
-        <v>8</v>
+        <v>16</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>49</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="36">
@@ -3969,67 +4185,73 @@
         <v>5</v>
       </c>
       <c r="H36" t="n">
-        <v>178</v>
+        <v>726</v>
       </c>
       <c r="I36" t="n">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="J36" t="n">
-        <v>176</v>
+        <v>701</v>
       </c>
       <c r="K36" t="n">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="L36" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="M36" t="n">
-        <v>9.869999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>7.98</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>1828</v>
+        <v>9367</v>
       </c>
       <c r="P36" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q36" t="n">
-        <v>95.2</v>
+        <v>91.7</v>
       </c>
       <c r="R36" t="n">
-        <v>95.2</v>
+        <v>91.7</v>
       </c>
       <c r="S36" t="n">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U36" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V36" t="n">
-        <v>13.5</v>
+        <v>2.78</v>
       </c>
       <c r="W36" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="X36" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="Y36" t="n">
-        <v>41</v>
+        <v>254</v>
       </c>
       <c r="Z36" t="n">
-        <v>50</v>
+        <v>308</v>
       </c>
       <c r="AA36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AB36" t="n">
-        <v>8</v>
+        <v>22</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="37">
@@ -4067,67 +4289,73 @@
         <v>6</v>
       </c>
       <c r="H37" t="n">
-        <v>324</v>
+        <v>510</v>
       </c>
       <c r="I37" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="J37" t="n">
-        <v>325</v>
+        <v>481</v>
       </c>
       <c r="K37" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.3</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>8.76</v>
+        <v>8.68</v>
       </c>
       <c r="N37" t="n">
-        <v>8.09</v>
+        <v>7.86</v>
       </c>
       <c r="O37" t="n">
-        <v>3985</v>
+        <v>6055</v>
       </c>
       <c r="P37" t="n">
         <v>21</v>
       </c>
       <c r="Q37" t="n">
-        <v>103.6</v>
+        <v>97.2</v>
       </c>
       <c r="R37" t="n">
-        <v>103.6</v>
+        <v>97.2</v>
       </c>
       <c r="S37" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U37" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V37" t="n">
-        <v>10.5</v>
+        <v>2.33</v>
       </c>
       <c r="W37" t="n">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="X37" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="Y37" t="n">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="Z37" t="n">
-        <v>102</v>
+        <v>190</v>
       </c>
       <c r="AA37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC37" t="n">
         <v>20</v>
       </c>
-      <c r="AB37" t="n">
-        <v>14</v>
+      <c r="AD37" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="38">
@@ -4165,67 +4393,73 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>4184</v>
+        <v>946</v>
       </c>
       <c r="I38" t="n">
-        <v>906</v>
+        <v>164</v>
       </c>
       <c r="J38" t="n">
-        <v>4193</v>
+        <v>977</v>
       </c>
       <c r="K38" t="n">
-        <v>874</v>
+        <v>159</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.2</v>
+        <v>-3.2</v>
       </c>
       <c r="M38" t="n">
-        <v>9.529999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="N38" t="n">
-        <v>8.539999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="O38" t="n">
-        <v>44015</v>
+        <v>10771</v>
       </c>
       <c r="P38" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q38" t="n">
-        <v>98.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="R38" t="n">
-        <v>98.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="S38" t="n">
-        <v>677</v>
+        <v>113</v>
       </c>
       <c r="T38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U38" t="n">
-        <v>93.3</v>
+        <v>80</v>
       </c>
       <c r="V38" t="n">
-        <v>1.86</v>
+        <v>2.75</v>
       </c>
       <c r="W38" t="n">
-        <v>951</v>
+        <v>132</v>
       </c>
       <c r="X38" t="n">
-        <v>1138</v>
+        <v>189</v>
       </c>
       <c r="Y38" t="n">
-        <v>996</v>
+        <v>352</v>
       </c>
       <c r="Z38" t="n">
-        <v>1099</v>
+        <v>273</v>
       </c>
       <c r="AA38" t="n">
-        <v>209</v>
+        <v>30</v>
       </c>
       <c r="AB38" t="n">
-        <v>266</v>
+        <v>40</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>53</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -4263,67 +4497,73 @@
         <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>3916</v>
+        <v>918</v>
       </c>
       <c r="I39" t="n">
-        <v>800</v>
+        <v>174</v>
       </c>
       <c r="J39" t="n">
-        <v>3833</v>
+        <v>899</v>
       </c>
       <c r="K39" t="n">
-        <v>759</v>
+        <v>171</v>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M39" t="n">
-        <v>9.130000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>9.279999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="O39" t="n">
-        <v>45642</v>
+        <v>10488</v>
       </c>
       <c r="P39" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q39" t="n">
-        <v>95</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R39" t="n">
-        <v>95</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="S39" t="n">
-        <v>573</v>
+        <v>129</v>
       </c>
       <c r="T39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U39" t="n">
-        <v>73.3</v>
+        <v>90</v>
       </c>
       <c r="V39" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>977</v>
+        <v>183</v>
       </c>
       <c r="X39" t="n">
-        <v>1071</v>
+        <v>192</v>
       </c>
       <c r="Y39" t="n">
-        <v>900</v>
+        <v>273</v>
       </c>
       <c r="Z39" t="n">
-        <v>968</v>
+        <v>270</v>
       </c>
       <c r="AA39" t="n">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="AB39" t="n">
-        <v>219</v>
+        <v>35</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>49</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="40">
@@ -4361,67 +4601,73 @@
         <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>4124</v>
+        <v>940</v>
       </c>
       <c r="I40" t="n">
-        <v>755</v>
+        <v>152</v>
       </c>
       <c r="J40" t="n">
-        <v>4193</v>
+        <v>963</v>
       </c>
       <c r="K40" t="n">
-        <v>741</v>
+        <v>141</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="M40" t="n">
-        <v>9.32</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>8.890000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="O40" t="n">
-        <v>46852</v>
+        <v>11394</v>
       </c>
       <c r="P40" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q40" t="n">
-        <v>101.3</v>
+        <v>106.3</v>
       </c>
       <c r="R40" t="n">
-        <v>101.3</v>
+        <v>106.3</v>
       </c>
       <c r="S40" t="n">
-        <v>537</v>
+        <v>107</v>
       </c>
       <c r="T40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U40" t="n">
-        <v>73.3</v>
+        <v>90</v>
       </c>
       <c r="V40" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>1055</v>
+        <v>139</v>
       </c>
       <c r="X40" t="n">
-        <v>1091</v>
+        <v>113</v>
       </c>
       <c r="Y40" t="n">
-        <v>940</v>
+        <v>398</v>
       </c>
       <c r="Z40" t="n">
-        <v>1038</v>
+        <v>290</v>
       </c>
       <c r="AA40" t="n">
-        <v>189</v>
+        <v>32</v>
       </c>
       <c r="AB40" t="n">
-        <v>220</v>
+        <v>20</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="41">
@@ -4459,67 +4705,73 @@
         <v>4</v>
       </c>
       <c r="H41" t="n">
-        <v>4194</v>
+        <v>776</v>
       </c>
       <c r="I41" t="n">
-        <v>850</v>
+        <v>127</v>
       </c>
       <c r="J41" t="n">
-        <v>4302</v>
+        <v>768</v>
       </c>
       <c r="K41" t="n">
-        <v>812</v>
+        <v>119</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>9.41</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>8.93</v>
+        <v>9.34</v>
       </c>
       <c r="O41" t="n">
-        <v>45968</v>
+        <v>9353</v>
       </c>
       <c r="P41" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q41" t="n">
-        <v>94.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R41" t="n">
-        <v>94.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="S41" t="n">
-        <v>615</v>
+        <v>84</v>
       </c>
       <c r="T41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U41" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="V41" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="W41" t="n">
-        <v>967</v>
+        <v>108</v>
       </c>
       <c r="X41" t="n">
-        <v>979</v>
+        <v>97</v>
       </c>
       <c r="Y41" t="n">
-        <v>1190</v>
+        <v>248</v>
       </c>
       <c r="Z41" t="n">
-        <v>1058</v>
+        <v>323</v>
       </c>
       <c r="AA41" t="n">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="AB41" t="n">
-        <v>194</v>
+        <v>25</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>41</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="42">
@@ -4557,67 +4809,73 @@
         <v>5</v>
       </c>
       <c r="H42" t="n">
-        <v>4464</v>
+        <v>874</v>
       </c>
       <c r="I42" t="n">
-        <v>865</v>
+        <v>173</v>
       </c>
       <c r="J42" t="n">
-        <v>4461</v>
+        <v>840</v>
       </c>
       <c r="K42" t="n">
-        <v>822</v>
+        <v>156</v>
       </c>
       <c r="L42" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>9.48</v>
+        <v>8.82</v>
       </c>
       <c r="N42" t="n">
-        <v>8.19</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>50085</v>
+        <v>10540</v>
       </c>
       <c r="P42" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q42" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R42" t="n">
-        <v>97.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S42" t="n">
-        <v>622</v>
+        <v>112</v>
       </c>
       <c r="T42" t="n">
+        <v>10</v>
+      </c>
+      <c r="U42" t="n">
+        <v>90</v>
+      </c>
+      <c r="V42" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="W42" t="n">
+        <v>107</v>
+      </c>
+      <c r="X42" t="n">
+        <v>114</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>300</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>353</v>
+      </c>
+      <c r="AA42" t="n">
         <v>15</v>
       </c>
-      <c r="U42" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1078</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1172</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1105</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1109</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>177</v>
-      </c>
       <c r="AB42" t="n">
-        <v>244</v>
+        <v>19</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="43">
@@ -4655,67 +4913,73 @@
         <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>4488</v>
+        <v>746</v>
       </c>
       <c r="I43" t="n">
-        <v>828</v>
+        <v>143</v>
       </c>
       <c r="J43" t="n">
-        <v>4396</v>
+        <v>733</v>
       </c>
       <c r="K43" t="n">
-        <v>813</v>
+        <v>138</v>
       </c>
       <c r="L43" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="M43" t="n">
-        <v>8.94</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>8.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>52758</v>
+        <v>8484</v>
       </c>
       <c r="P43" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="Q43" t="n">
-        <v>92.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="R43" t="n">
-        <v>92.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="S43" t="n">
-        <v>599</v>
+        <v>99</v>
       </c>
       <c r="T43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="U43" t="n">
-        <v>93.3</v>
+        <v>80</v>
       </c>
       <c r="V43" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="W43" t="n">
-        <v>1091</v>
+        <v>82</v>
       </c>
       <c r="X43" t="n">
-        <v>1146</v>
+        <v>84</v>
       </c>
       <c r="Y43" t="n">
-        <v>1135</v>
+        <v>328</v>
       </c>
       <c r="Z43" t="n">
-        <v>1116</v>
+        <v>252</v>
       </c>
       <c r="AA43" t="n">
-        <v>202</v>
+        <v>16</v>
       </c>
       <c r="AB43" t="n">
-        <v>206</v>
+        <v>18</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>67</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="44">
@@ -4753,67 +5017,73 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>3354</v>
+        <v>1300</v>
       </c>
       <c r="I44" t="n">
-        <v>702</v>
+        <v>267</v>
       </c>
       <c r="J44" t="n">
-        <v>3324</v>
+        <v>1282</v>
       </c>
       <c r="K44" t="n">
-        <v>694</v>
+        <v>272</v>
       </c>
       <c r="L44" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="M44" t="n">
-        <v>8.65</v>
+        <v>9.06</v>
       </c>
       <c r="N44" t="n">
-        <v>8.26</v>
+        <v>8.48</v>
       </c>
       <c r="O44" t="n">
-        <v>41324</v>
+        <v>14714</v>
       </c>
       <c r="P44" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Q44" t="n">
-        <v>102.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="R44" t="n">
-        <v>102.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="S44" t="n">
-        <v>527</v>
+        <v>207</v>
       </c>
       <c r="T44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U44" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V44" t="n">
-        <v>3.11</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>911</v>
+        <v>293</v>
       </c>
       <c r="X44" t="n">
-        <v>724</v>
+        <v>282</v>
       </c>
       <c r="Y44" t="n">
-        <v>863</v>
+        <v>389</v>
       </c>
       <c r="Z44" t="n">
-        <v>856</v>
+        <v>336</v>
       </c>
       <c r="AA44" t="n">
-        <v>160</v>
+        <v>67</v>
       </c>
       <c r="AB44" t="n">
-        <v>169</v>
+        <v>61</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>84</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="45">
@@ -4851,67 +5121,73 @@
         <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>2416</v>
+        <v>1042</v>
       </c>
       <c r="I45" t="n">
-        <v>468</v>
+        <v>209</v>
       </c>
       <c r="J45" t="n">
-        <v>2473</v>
+        <v>1070</v>
       </c>
       <c r="K45" t="n">
-        <v>448</v>
+        <v>204</v>
       </c>
       <c r="L45" t="n">
-        <v>-2.3</v>
+        <v>-2.6</v>
       </c>
       <c r="M45" t="n">
-        <v>9.56</v>
+        <v>8.94</v>
       </c>
       <c r="N45" t="n">
-        <v>8.970000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>25239</v>
+        <v>12708</v>
       </c>
       <c r="P45" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="Q45" t="n">
-        <v>107</v>
+        <v>92.5</v>
       </c>
       <c r="R45" t="n">
-        <v>107</v>
+        <v>92.5</v>
       </c>
       <c r="S45" t="n">
-        <v>337</v>
+        <v>136</v>
       </c>
       <c r="T45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U45" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="V45" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="W45" t="n">
-        <v>574</v>
+        <v>307</v>
       </c>
       <c r="X45" t="n">
-        <v>571</v>
+        <v>281</v>
       </c>
       <c r="Y45" t="n">
-        <v>588</v>
+        <v>195</v>
       </c>
       <c r="Z45" t="n">
-        <v>683</v>
+        <v>259</v>
       </c>
       <c r="AA45" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AB45" t="n">
-        <v>112</v>
+        <v>68</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="46">
@@ -4949,67 +5225,73 @@
         <v>3</v>
       </c>
       <c r="H46" t="n">
-        <v>2426</v>
+        <v>1264</v>
       </c>
       <c r="I46" t="n">
-        <v>456</v>
+        <v>239</v>
       </c>
       <c r="J46" t="n">
-        <v>2426</v>
+        <v>1223</v>
       </c>
       <c r="K46" t="n">
-        <v>446</v>
+        <v>235</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M46" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="N46" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="O46" t="n">
+        <v>14872</v>
+      </c>
+      <c r="P46" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="R46" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="S46" t="n">
+        <v>168</v>
+      </c>
+      <c r="T46" t="n">
         <v>10</v>
       </c>
-      <c r="N46" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="O46" t="n">
-        <v>24556</v>
-      </c>
-      <c r="P46" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="R46" t="n">
-        <v>105.3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>317</v>
-      </c>
-      <c r="T46" t="n">
-        <v>9</v>
-      </c>
       <c r="U46" t="n">
-        <v>88.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="V46" t="n">
-        <v>3.25</v>
+        <v>2.67</v>
       </c>
       <c r="W46" t="n">
-        <v>662</v>
+        <v>311</v>
       </c>
       <c r="X46" t="n">
-        <v>571</v>
+        <v>312</v>
       </c>
       <c r="Y46" t="n">
-        <v>605</v>
+        <v>377</v>
       </c>
       <c r="Z46" t="n">
-        <v>588</v>
+        <v>264</v>
       </c>
       <c r="AA46" t="n">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="AB46" t="n">
-        <v>103</v>
+        <v>57</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>69</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="47">
@@ -5047,67 +5329,73 @@
         <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>2790</v>
+        <v>1145</v>
       </c>
       <c r="I47" t="n">
-        <v>532</v>
+        <v>250</v>
       </c>
       <c r="J47" t="n">
-        <v>2814</v>
+        <v>1137</v>
       </c>
       <c r="K47" t="n">
-        <v>508</v>
+        <v>247</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M47" t="n">
-        <v>8.890000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>8.109999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>31504</v>
+        <v>12991</v>
       </c>
       <c r="P47" t="n">
         <v>19</v>
       </c>
       <c r="Q47" t="n">
-        <v>103.6</v>
+        <v>106.5</v>
       </c>
       <c r="R47" t="n">
-        <v>103.6</v>
+        <v>106.5</v>
       </c>
       <c r="S47" t="n">
-        <v>394</v>
+        <v>183</v>
       </c>
       <c r="T47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U47" t="n">
-        <v>88.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="V47" t="n">
         <v>2.38</v>
       </c>
       <c r="W47" t="n">
-        <v>755</v>
+        <v>489</v>
       </c>
       <c r="X47" t="n">
-        <v>711</v>
+        <v>318</v>
       </c>
       <c r="Y47" t="n">
-        <v>625</v>
+        <v>199</v>
       </c>
       <c r="Z47" t="n">
-        <v>699</v>
+        <v>139</v>
       </c>
       <c r="AA47" t="n">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="AB47" t="n">
-        <v>169</v>
+        <v>63</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>45</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -5145,67 +5433,73 @@
         <v>5</v>
       </c>
       <c r="H48" t="n">
-        <v>2291</v>
+        <v>1151</v>
       </c>
       <c r="I48" t="n">
-        <v>466</v>
+        <v>225</v>
       </c>
       <c r="J48" t="n">
-        <v>2263</v>
+        <v>1145</v>
       </c>
       <c r="K48" t="n">
-        <v>452</v>
+        <v>231</v>
       </c>
       <c r="L48" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="M48" t="n">
-        <v>9.359999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>8.99</v>
+        <v>9.24</v>
       </c>
       <c r="O48" t="n">
-        <v>24328</v>
+        <v>13508</v>
       </c>
       <c r="P48" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="n">
-        <v>101.3</v>
+        <v>101.8</v>
       </c>
       <c r="R48" t="n">
-        <v>101.3</v>
+        <v>101.8</v>
       </c>
       <c r="S48" t="n">
-        <v>338</v>
+        <v>168</v>
       </c>
       <c r="T48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U48" t="n">
         <v>100</v>
       </c>
       <c r="V48" t="n">
-        <v>3.11</v>
+        <v>2.1</v>
       </c>
       <c r="W48" t="n">
-        <v>584</v>
+        <v>231</v>
       </c>
       <c r="X48" t="n">
-        <v>595</v>
+        <v>195</v>
       </c>
       <c r="Y48" t="n">
-        <v>559</v>
+        <v>289</v>
       </c>
       <c r="Z48" t="n">
-        <v>553</v>
+        <v>436</v>
       </c>
       <c r="AA48" t="n">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="AB48" t="n">
-        <v>136</v>
+        <v>41</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>54</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="49">
@@ -5243,67 +5537,73 @@
         <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>3343</v>
+        <v>1333</v>
       </c>
       <c r="I49" t="n">
-        <v>627</v>
+        <v>274</v>
       </c>
       <c r="J49" t="n">
-        <v>3274</v>
+        <v>1311</v>
       </c>
       <c r="K49" t="n">
-        <v>606</v>
+        <v>255</v>
       </c>
       <c r="L49" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="M49" t="n">
-        <v>9.300000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>9.539999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>38082</v>
+        <v>14414</v>
       </c>
       <c r="P49" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Q49" t="n">
-        <v>90.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R49" t="n">
-        <v>90.7</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S49" t="n">
-        <v>438</v>
+        <v>197</v>
       </c>
       <c r="T49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U49" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V49" t="n">
-        <v>3.11</v>
+        <v>2.44</v>
       </c>
       <c r="W49" t="n">
-        <v>828</v>
+        <v>393</v>
       </c>
       <c r="X49" t="n">
-        <v>969</v>
+        <v>360</v>
       </c>
       <c r="Y49" t="n">
-        <v>704</v>
+        <v>258</v>
       </c>
       <c r="Z49" t="n">
-        <v>842</v>
+        <v>322</v>
       </c>
       <c r="AA49" t="n">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="AB49" t="n">
-        <v>187</v>
+        <v>57</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="50">
@@ -5341,40 +5641,40 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>2769</v>
+        <v>1082</v>
       </c>
       <c r="I50" t="n">
-        <v>573</v>
+        <v>173</v>
       </c>
       <c r="J50" t="n">
-        <v>2743</v>
+        <v>1070</v>
       </c>
       <c r="K50" t="n">
-        <v>529</v>
+        <v>168</v>
       </c>
       <c r="L50" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="M50" t="n">
-        <v>8.800000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>8.98</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>32371</v>
+        <v>13447</v>
       </c>
       <c r="P50" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q50" t="n">
-        <v>93.2</v>
+        <v>106.2</v>
       </c>
       <c r="R50" t="n">
-        <v>93.2</v>
+        <v>106.2</v>
       </c>
       <c r="S50" t="n">
-        <v>376</v>
+        <v>120</v>
       </c>
       <c r="T50" t="n">
         <v>10</v>
@@ -5383,25 +5683,31 @@
         <v>90</v>
       </c>
       <c r="V50" t="n">
-        <v>2.11</v>
+        <v>3.11</v>
       </c>
       <c r="W50" t="n">
-        <v>761</v>
+        <v>267</v>
       </c>
       <c r="X50" t="n">
-        <v>696</v>
+        <v>271</v>
       </c>
       <c r="Y50" t="n">
-        <v>686</v>
+        <v>298</v>
       </c>
       <c r="Z50" t="n">
-        <v>626</v>
+        <v>246</v>
       </c>
       <c r="AA50" t="n">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="AB50" t="n">
-        <v>158</v>
+        <v>55</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>48</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="51">
@@ -5439,67 +5745,73 @@
         <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>2505</v>
+        <v>1128</v>
       </c>
       <c r="I51" t="n">
-        <v>466</v>
+        <v>218</v>
       </c>
       <c r="J51" t="n">
-        <v>2514</v>
+        <v>1123</v>
       </c>
       <c r="K51" t="n">
-        <v>463</v>
+        <v>218</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="M51" t="n">
-        <v>8.800000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>9.26</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>28002</v>
+        <v>13460</v>
       </c>
       <c r="P51" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q51" t="n">
-        <v>97.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R51" t="n">
-        <v>97.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="S51" t="n">
-        <v>331</v>
+        <v>161</v>
       </c>
       <c r="T51" t="n">
         <v>10</v>
       </c>
       <c r="U51" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="V51" t="n">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="W51" t="n">
-        <v>620</v>
+        <v>213</v>
       </c>
       <c r="X51" t="n">
-        <v>579</v>
+        <v>264</v>
       </c>
       <c r="Y51" t="n">
-        <v>578</v>
+        <v>284</v>
       </c>
       <c r="Z51" t="n">
-        <v>728</v>
+        <v>367</v>
       </c>
       <c r="AA51" t="n">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="AB51" t="n">
-        <v>107</v>
+        <v>49</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>45</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>85</v>
       </c>
     </row>
     <row r="52">
@@ -5537,67 +5849,73 @@
         <v>3</v>
       </c>
       <c r="H52" t="n">
-        <v>2657</v>
+        <v>1098</v>
       </c>
       <c r="I52" t="n">
-        <v>584</v>
+        <v>230</v>
       </c>
       <c r="J52" t="n">
-        <v>2531</v>
+        <v>1077</v>
       </c>
       <c r="K52" t="n">
-        <v>573</v>
+        <v>223</v>
       </c>
       <c r="L52" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="M52" t="n">
-        <v>9.289999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="N52" t="n">
-        <v>9.56</v>
+        <v>7.78</v>
       </c>
       <c r="O52" t="n">
-        <v>28862</v>
+        <v>12873</v>
       </c>
       <c r="P52" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q52" t="n">
-        <v>102.2</v>
+        <v>101.3</v>
       </c>
       <c r="R52" t="n">
-        <v>102.2</v>
+        <v>101.3</v>
       </c>
       <c r="S52" t="n">
-        <v>429</v>
+        <v>171</v>
       </c>
       <c r="T52" t="n">
         <v>10</v>
       </c>
       <c r="U52" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="V52" t="n">
-        <v>2.86</v>
+        <v>2.11</v>
       </c>
       <c r="W52" t="n">
-        <v>726</v>
+        <v>209</v>
       </c>
       <c r="X52" t="n">
-        <v>657</v>
+        <v>257</v>
       </c>
       <c r="Y52" t="n">
-        <v>616</v>
+        <v>263</v>
       </c>
       <c r="Z52" t="n">
-        <v>658</v>
+        <v>369</v>
       </c>
       <c r="AA52" t="n">
-        <v>188</v>
+        <v>51</v>
       </c>
       <c r="AB52" t="n">
-        <v>134</v>
+        <v>50</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>46</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="53">
@@ -5635,40 +5953,40 @@
         <v>4</v>
       </c>
       <c r="H53" t="n">
-        <v>2357</v>
+        <v>1476</v>
       </c>
       <c r="I53" t="n">
-        <v>428</v>
+        <v>302</v>
       </c>
       <c r="J53" t="n">
-        <v>2332</v>
+        <v>1423</v>
       </c>
       <c r="K53" t="n">
-        <v>417</v>
+        <v>307</v>
       </c>
       <c r="L53" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="M53" t="n">
-        <v>9.66</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>9.609999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>25462</v>
+        <v>18071</v>
       </c>
       <c r="P53" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Q53" t="n">
-        <v>109.4</v>
+        <v>94.8</v>
       </c>
       <c r="R53" t="n">
-        <v>109.4</v>
+        <v>94.8</v>
       </c>
       <c r="S53" t="n">
-        <v>315</v>
+        <v>215</v>
       </c>
       <c r="T53" t="n">
         <v>10</v>
@@ -5677,25 +5995,31 @@
         <v>80</v>
       </c>
       <c r="V53" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="W53" t="n">
-        <v>609</v>
+        <v>435</v>
       </c>
       <c r="X53" t="n">
-        <v>585</v>
+        <v>399</v>
       </c>
       <c r="Y53" t="n">
-        <v>557</v>
+        <v>342</v>
       </c>
       <c r="Z53" t="n">
-        <v>606</v>
+        <v>300</v>
       </c>
       <c r="AA53" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="AB53" t="n">
-        <v>104</v>
+        <v>62</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>86</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -5733,40 +6057,40 @@
         <v>5</v>
       </c>
       <c r="H54" t="n">
-        <v>2421</v>
+        <v>956</v>
       </c>
       <c r="I54" t="n">
-        <v>439</v>
+        <v>186</v>
       </c>
       <c r="J54" t="n">
-        <v>2343</v>
+        <v>988</v>
       </c>
       <c r="K54" t="n">
-        <v>432</v>
+        <v>176</v>
       </c>
       <c r="L54" t="n">
-        <v>3.3</v>
+        <v>-3.2</v>
       </c>
       <c r="M54" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="N54" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="O54" t="n">
-        <v>27699</v>
+        <v>9628</v>
       </c>
       <c r="P54" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q54" t="n">
-        <v>101.7</v>
+        <v>96.8</v>
       </c>
       <c r="R54" t="n">
-        <v>101.7</v>
+        <v>96.8</v>
       </c>
       <c r="S54" t="n">
-        <v>312</v>
+        <v>131</v>
       </c>
       <c r="T54" t="n">
         <v>10</v>
@@ -5775,25 +6099,31 @@
         <v>100</v>
       </c>
       <c r="V54" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="W54" t="n">
-        <v>540</v>
+        <v>188</v>
       </c>
       <c r="X54" t="n">
-        <v>690</v>
+        <v>198</v>
       </c>
       <c r="Y54" t="n">
-        <v>606</v>
+        <v>318</v>
       </c>
       <c r="Z54" t="n">
-        <v>585</v>
+        <v>252</v>
       </c>
       <c r="AA54" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="AB54" t="n">
-        <v>101</v>
+        <v>33</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>56</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="55">
@@ -5831,67 +6161,73 @@
         <v>6</v>
       </c>
       <c r="H55" t="n">
-        <v>1915</v>
+        <v>1052</v>
       </c>
       <c r="I55" t="n">
-        <v>332</v>
+        <v>216</v>
       </c>
       <c r="J55" t="n">
-        <v>1827</v>
+        <v>1040</v>
       </c>
       <c r="K55" t="n">
-        <v>313</v>
+        <v>213</v>
       </c>
       <c r="L55" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="M55" t="n">
-        <v>9.32</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>8.73</v>
+        <v>7.97</v>
       </c>
       <c r="O55" t="n">
-        <v>21859</v>
+        <v>11138</v>
       </c>
       <c r="P55" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q55" t="n">
-        <v>100.7</v>
+        <v>100.2</v>
       </c>
       <c r="R55" t="n">
-        <v>100.7</v>
+        <v>100.2</v>
       </c>
       <c r="S55" t="n">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="T55" t="n">
         <v>10</v>
       </c>
       <c r="U55" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="V55" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="W55" t="n">
-        <v>460</v>
+        <v>268</v>
       </c>
       <c r="X55" t="n">
-        <v>466</v>
+        <v>235</v>
       </c>
       <c r="Y55" t="n">
-        <v>495</v>
+        <v>270</v>
       </c>
       <c r="Z55" t="n">
-        <v>494</v>
+        <v>279</v>
       </c>
       <c r="AA55" t="n">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="AB55" t="n">
-        <v>79</v>
+        <v>54</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>60</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="56">
@@ -5929,67 +6265,73 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1417</v>
+        <v>1326</v>
       </c>
       <c r="I56" t="n">
-        <v>285</v>
+        <v>207</v>
       </c>
       <c r="J56" t="n">
-        <v>1471</v>
+        <v>1338</v>
       </c>
       <c r="K56" t="n">
-        <v>289</v>
+        <v>200</v>
       </c>
       <c r="L56" t="n">
-        <v>-3.7</v>
+        <v>-0.9</v>
       </c>
       <c r="M56" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="N56" t="n">
-        <v>8.19</v>
+        <v>9.15</v>
       </c>
       <c r="O56" t="n">
-        <v>16673</v>
+        <v>16985</v>
       </c>
       <c r="P56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q56" t="n">
-        <v>93.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R56" t="n">
-        <v>93.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S56" t="n">
-        <v>215</v>
+        <v>146</v>
       </c>
       <c r="T56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U56" t="n">
         <v>100</v>
       </c>
       <c r="V56" t="n">
-        <v>6.33</v>
+        <v>1.8</v>
       </c>
       <c r="W56" t="n">
-        <v>294</v>
+        <v>505</v>
       </c>
       <c r="X56" t="n">
-        <v>319</v>
+        <v>448</v>
       </c>
       <c r="Y56" t="n">
-        <v>328</v>
+        <v>176</v>
       </c>
       <c r="Z56" t="n">
-        <v>476</v>
+        <v>197</v>
       </c>
       <c r="AA56" t="n">
+        <v>73</v>
+      </c>
+      <c r="AB56" t="n">
         <v>64</v>
       </c>
-      <c r="AB56" t="n">
-        <v>78</v>
+      <c r="AC56" t="n">
+        <v>37</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="57">
@@ -6027,67 +6369,73 @@
         <v>2</v>
       </c>
       <c r="H57" t="n">
-        <v>804</v>
+        <v>683</v>
       </c>
       <c r="I57" t="n">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="J57" t="n">
-        <v>793</v>
+        <v>646</v>
       </c>
       <c r="K57" t="n">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="L57" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="M57" t="n">
-        <v>8.23</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>9.26</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>10067</v>
+        <v>8191</v>
       </c>
       <c r="P57" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Q57" t="n">
-        <v>97.5</v>
+        <v>100.5</v>
       </c>
       <c r="R57" t="n">
-        <v>97.5</v>
+        <v>100.5</v>
       </c>
       <c r="S57" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="T57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U57" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V57" t="n">
-        <v>8.67</v>
+        <v>2.22</v>
       </c>
       <c r="W57" t="n">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="X57" t="n">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="Y57" t="n">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="Z57" t="n">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="AA57" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="AB57" t="n">
-        <v>33</v>
+        <v>47</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="58">
@@ -6125,67 +6473,73 @@
         <v>3</v>
       </c>
       <c r="H58" t="n">
-        <v>1107</v>
+        <v>1146</v>
       </c>
       <c r="I58" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="J58" t="n">
-        <v>1076</v>
+        <v>1148</v>
       </c>
       <c r="K58" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="L58" t="n">
-        <v>2.9</v>
+        <v>-0.2</v>
       </c>
       <c r="M58" t="n">
-        <v>8.279999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>9.949999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>13452</v>
+        <v>13533</v>
       </c>
       <c r="P58" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q58" t="n">
-        <v>89.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R58" t="n">
-        <v>89.09999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S58" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U58" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V58" t="n">
-        <v>8</v>
+        <v>3.11</v>
       </c>
       <c r="W58" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="X58" t="n">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="Y58" t="n">
-        <v>246</v>
+        <v>327</v>
       </c>
       <c r="Z58" t="n">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="AA58" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="AB58" t="n">
-        <v>46</v>
+        <v>37</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="59">
@@ -6223,67 +6577,73 @@
         <v>4</v>
       </c>
       <c r="H59" t="n">
-        <v>1422</v>
+        <v>1438</v>
       </c>
       <c r="I59" t="n">
-        <v>261</v>
+        <v>304</v>
       </c>
       <c r="J59" t="n">
-        <v>1429</v>
+        <v>1457</v>
       </c>
       <c r="K59" t="n">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.5</v>
+        <v>-1.3</v>
       </c>
       <c r="M59" t="n">
-        <v>8.960000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>9.369999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="O59" t="n">
-        <v>16362</v>
+        <v>15364</v>
       </c>
       <c r="P59" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q59" t="n">
-        <v>95.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R59" t="n">
-        <v>95.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="S59" t="n">
-        <v>186</v>
+        <v>226</v>
       </c>
       <c r="T59" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U59" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V59" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W59" t="n">
-        <v>235</v>
+        <v>393</v>
       </c>
       <c r="X59" t="n">
-        <v>471</v>
+        <v>408</v>
       </c>
       <c r="Y59" t="n">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="Z59" t="n">
-        <v>408</v>
+        <v>348</v>
       </c>
       <c r="AA59" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="AB59" t="n">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>54</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="60">
@@ -6321,67 +6681,73 @@
         <v>5</v>
       </c>
       <c r="H60" t="n">
-        <v>1024</v>
+        <v>824</v>
       </c>
       <c r="I60" t="n">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="J60" t="n">
-        <v>997</v>
+        <v>840</v>
       </c>
       <c r="K60" t="n">
-        <v>211</v>
+        <v>127</v>
       </c>
       <c r="L60" t="n">
-        <v>2.7</v>
+        <v>-1.9</v>
       </c>
       <c r="M60" t="n">
-        <v>9.130000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>8.68</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>10757</v>
+        <v>9202</v>
       </c>
       <c r="P60" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q60" t="n">
-        <v>101.4</v>
+        <v>100.7</v>
       </c>
       <c r="R60" t="n">
-        <v>101.4</v>
+        <v>100.7</v>
       </c>
       <c r="S60" t="n">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="T60" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U60" t="n">
         <v>100</v>
       </c>
       <c r="V60" t="n">
-        <v>6.67</v>
+        <v>2.1</v>
       </c>
       <c r="W60" t="n">
-        <v>295</v>
+        <v>176</v>
       </c>
       <c r="X60" t="n">
-        <v>275</v>
+        <v>149</v>
       </c>
       <c r="Y60" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Z60" t="n">
-        <v>255</v>
+        <v>302</v>
       </c>
       <c r="AA60" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AB60" t="n">
-        <v>68</v>
+        <v>27</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="61">
@@ -6419,67 +6785,73 @@
         <v>6</v>
       </c>
       <c r="H61" t="n">
-        <v>749</v>
+        <v>1381</v>
       </c>
       <c r="I61" t="n">
-        <v>157</v>
+        <v>257</v>
       </c>
       <c r="J61" t="n">
-        <v>749</v>
+        <v>1426</v>
       </c>
       <c r="K61" t="n">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>-3.2</v>
       </c>
       <c r="M61" t="n">
-        <v>9.77</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>9.1</v>
+        <v>8.91</v>
       </c>
       <c r="O61" t="n">
-        <v>8401</v>
+        <v>15824</v>
       </c>
       <c r="P61" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q61" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="R61" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="S61" t="n">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="T61" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U61" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="V61" t="n">
-        <v>6.33</v>
+        <v>2.44</v>
       </c>
       <c r="W61" t="n">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="X61" t="n">
-        <v>177</v>
+        <v>300</v>
       </c>
       <c r="Y61" t="n">
-        <v>163</v>
+        <v>398</v>
       </c>
       <c r="Z61" t="n">
-        <v>239</v>
+        <v>452</v>
       </c>
       <c r="AA61" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="AB61" t="n">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>71</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
